--- a/docs/산출물/09_한결공조_AS관리_통합테스트결과서_V1.1.xlsx
+++ b/docs/산출물/09_한결공조_AS관리_통합테스트결과서_V1.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\my-first-project\docs\산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FF43F9-FB38-44B9-8E42-FB7D05A59FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5891407-B4DB-429F-AE1E-0A39B9F79D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="426">
   <si>
     <t>프로젝트명</t>
   </si>
@@ -1441,735 +1441,744 @@
     <t>IT-WO-003</t>
   </si>
   <si>
-    <t>남은 수량보다 많이 입력하면 저장이 거부되고 재고 이동으로 보충한 뒤에는 저장되는지 확인</t>
+    <t>한 사이클</t>
+  </si>
+  <si>
+    <t>접수 → 배정 → 부품 → 완료 → 종결</t>
+  </si>
+  <si>
+    <t>IT-WO-004</t>
+  </si>
+  <si>
+    <t>상담원 접수부터 종결까지 세 사용자가 실제 화면으로 한 번에 처리되는지 확인</t>
+  </si>
+  <si>
+    <t>• 이서연·김병철·최민호 로그인</t>
+  </si>
+  <si>
+    <t>• 가상 착신 010-1111-2002 → 중복 경고 00001028 [기존 접수 열기] → 김병철 [기사 배정] → 최민호 수락·도착·부품 → 완료 → 종결</t>
+  </si>
+  <si>
+    <t>• 새 접수 없이 기존 접수로 처리, 출동 생성·부품 ERP 전송·승인 불필요 안내, 종결 후 수정 잠김</t>
+  </si>
+  <si>
+    <t>2026-10-16: 00001028 → 출동 00000049 → 냉매 R-404A 0.5kg(차량 14.5→14.0, ERP 완료) → 승인 불필요 안내(₩20,000 / 기준 ₩500,000) → 출동 완료 → 접수 완료 → 종결 → 수정 시 잠김 경고. 실습 중 결함 1건(출장비 빈칸) 수정</t>
+  </si>
+  <si>
+    <t>접수 자동 완료</t>
+  </si>
+  <si>
+    <t>접수 자동 완료 · 종결 대기 · BR-18</t>
+  </si>
+  <si>
+    <t>IT-WO-005</t>
+  </si>
+  <si>
+    <t>마지막 열린 출동이 완료되면 접수가 자동 완료되고 센터장 "종결 대기 접수"에 보이며, 열린 출동이 있으면 완료·종결할 수 없는지 확인</t>
+  </si>
+  <si>
+    <t>• 처리 중 접수 + 출동 1건</t>
+  </si>
+  <si>
+    <t>• 출동 완료 → 센터장 홈 확인</t>
+  </si>
+  <si>
+    <t>• 접수 완료(열린 0·완료 1), 종결 대기 목록 표시, 열린 출동이 있으면 완료·종결 거부</t>
+  </si>
+  <si>
+    <t>2026-10-18 시연 준비: 출동 00000064·00000065 완료 → 접수 00001996·00001997 자동 완료(열린 0·완료 1), 종결 대기 3건(조회). 리셋 검증: 종결 → 완료 복원. 열린 출동 거부는 Apex 테스트 CaseWorkOrderStatsServiceTest(상담원 runAs) Pass</t>
+  </si>
+  <si>
+    <t>재고 공유</t>
+  </si>
+  <si>
+    <t>다른 센터 창고 재고 비공개</t>
+  </si>
+  <si>
+    <t>IT-WO-006</t>
+  </si>
+  <si>
+    <t>경기남부 기사·센터장은 경기남부 창고 재고만 읽고 다른 센터(서울) 창고 재고는 못 보는지 확인</t>
+  </si>
+  <si>
+    <t>• 검증용 서울 창고 위치·재고 1건(조회 후 삭제)
+• 조건 기준 공유 규칙 HG_GyeonggiSouth_Warehouse_Stock_Tech</t>
+  </si>
+  <si>
+    <t>• UserRecordAccess(HasReadAccess) × 김병철·최민호·이서연</t>
+  </si>
+  <si>
+    <t>• 서울 창고 재고: 김병철·최민호 읽기 없음 / 경기남부 창고 재고 14건 읽기 유지</t>
+  </si>
+  <si>
+    <t>2026-10-16: 규칙 교체 전 결함(서울 창고 재고 읽기) 발견 → 조건 기준 규칙으로 교체 후 서울 창고 재고 김병철·최민호 읽기 없음, 경기남부 창고 재고 14건 유지, 상담원 전체 읽기 유지</t>
+  </si>
+  <si>
+    <t>결함 이력: 수정사항관리 · 재고 이동 공유 없음은 한계</t>
+  </si>
+  <si>
+    <t>PROCESS 3 · 출동 승인 (기사 · 센터장)</t>
+  </si>
+  <si>
+    <t>출동 승인 요청</t>
+  </si>
+  <si>
+    <t>승인 불필요 출동 안내</t>
+  </si>
+  <si>
+    <t>IT-APV-001</t>
+  </si>
+  <si>
+    <t>예외 무상이 없고 청구 합계가 기준 이하인 출동에서 [승인 요청]을 누르면 안내만 나오는지 확인</t>
+  </si>
+  <si>
+    <t>• 출동 00000038(500,000)·00000039(30,000)</t>
+  </si>
+  <si>
+    <t>• 빠른 작업 [승인 요청]</t>
+  </si>
+  <si>
+    <t>• "승인이 필요하지 않습니다" 안내</t>
+  </si>
+  <si>
+    <t>2026-10-16: 최민호 화면에서 "승인이 필요하지 않습니다" 안내 확인(Edwin)</t>
+  </si>
+  <si>
+    <t>기사 승인 요청 제출</t>
+  </si>
+  <si>
+    <t>IT-APV-002</t>
+  </si>
+  <si>
+    <t>기준 초과 출동에서 기사가 사유·고객 동의를 넣어 승인 요청 → 센터장에게 승인 요청이 가는지 확인</t>
+  </si>
+  <si>
+    <t>• 최민호(기사) · Manager = 김병철
+• 출동 00000037 청구 합계 1,200,000</t>
+  </si>
+  <si>
+    <t>• 사유 "고객 과실" · 고객 동의 체크</t>
+  </si>
+  <si>
+    <t>• 상태 승인 대기, 승인자 김병철</t>
+  </si>
+  <si>
+    <t>2026-10-15 17:46: 최민호 제출(사유 "고객 과실", 고객 동의 저장), 승인자 김병철 — org 승인 기록. 출동의 [승인 요청] 빠른 작업으로 제출(Edwin)</t>
+  </si>
+  <si>
+    <t>출동 승인</t>
+  </si>
+  <si>
+    <t>센터장 승인</t>
+  </si>
+  <si>
+    <t>IT-APV-003</t>
+  </si>
+  <si>
+    <t>센터장이 승인하면 출동이 도착 상태로 돌아오고 승인 상태가 승인으로 바뀌는지 확인</t>
+  </si>
+  <si>
+    <t>• IT-APV-002 이어서 · 김병철 로그인</t>
+  </si>
+  <si>
+    <t>• 승인 요청 → [승인]</t>
+  </si>
+  <si>
+    <t>• 승인 상태 Approved · 상태 Arrived</t>
+  </si>
+  <si>
+    <t>2026-10-15 17:47: 김병철 승인, 출동 00000037 승인 상태 Approved · 상태 Arrived(조회 확인)</t>
+  </si>
+  <si>
+    <t>반려 시 사유 필수 · 도착 복귀</t>
+  </si>
+  <si>
+    <t>IT-APV-004</t>
+  </si>
+  <si>
+    <t>기사 화면 [승인 요청] 표시</t>
+  </si>
+  <si>
+    <t>IT-APV-005</t>
+  </si>
+  <si>
+    <t>협력 기사의 출동 화면 강조 패널에 빠른 작업 [승인 요청]이 보이는지 확인</t>
+  </si>
+  <si>
+    <t>• 출동 레코드 화면 열기</t>
+  </si>
+  <si>
+    <t>• [승인 요청] 버튼 표시</t>
+  </si>
+  <si>
+    <t>2026-10-15 버튼 미표시 → 원인: 출동 피드 추적으로 빠른 작업이 Chatter 게시자 영역에 배치(페이지에 피드 없음). 강조 표시 패널을 동적 작업으로 전환 후 최민호 화면에서 표시 확인. Flow 실행 권한은 추가하지 않음(개별 Flow 접근만으로 동작)</t>
+  </si>
+  <si>
+    <t>결함 수정 후 재확인</t>
+  </si>
+  <si>
+    <t>승인 요청 요약 · 승인할 항목</t>
+  </si>
+  <si>
+    <t>IT-APV-006</t>
+  </si>
+  <si>
+    <t>기사가 제출하면 승인 요청 요약(이유·부품별 줄·사유·고객 동의·메모)이 제출 댓글·출동 필드에 남고, 센터장 홈 "승인할 항목"과 승인 화면 필드 13개로 판단할 수 있는지 확인</t>
+  </si>
+  <si>
+    <t>• [테스트] 접수 00001980 · 출동 00000050(₩850,000)</t>
+  </si>
+  <si>
+    <t>• 최민호 [승인 요청] 제출 → 김병철 홈 "승인할 항목" → 승인 화면</t>
+  </si>
+  <si>
+    <t>• 승인할 항목에 00000050 표시, 승인 화면 필드 13개, 제출자 댓글 = 요약</t>
+  </si>
+  <si>
+    <t>2026-10-16: 김병철 홈 "승인할 항목"에 00000050 표시, 승인 화면 필드·제출자 댓글(요약) 확인 → 회수, 테스트 데이터(접수 00001980·출동 00000050·사용 부품 2) 삭제</t>
+  </si>
+  <si>
+    <t>결함 이력: 수정사항관리(요약 줄바꿈)</t>
+  </si>
+  <si>
+    <t>PROCESS 4 · 외부 연동 (ERP · 주소)</t>
+  </si>
+  <si>
+    <t>도로명주소 검색</t>
+  </si>
+  <si>
+    <t>주소 검색 실제 호출</t>
+  </si>
+  <si>
+    <t>IT-IF-001</t>
+  </si>
+  <si>
+    <t>사업장 빠른 작업 "주소 검색"이 도로명주소 API를 호출해 결과를 보여 주는지 확인</t>
+  </si>
+  <si>
+    <t>• 승인키(보안 주체 HG_JusoPrincipal) 입력됨</t>
+  </si>
+  <si>
+    <t>• 검색어 "평택로 32"</t>
+  </si>
+  <si>
+    <t>• 결과 목록 · 더 보기</t>
+  </si>
+  <si>
+    <t>2026-10-13 실제 호출 확인, 2026-10-15 "평택로 32" 24건 중 10건 표시(화면 캡처), 2026-10-18 이서연 화면 "판교역로 166" 결과 표시</t>
+  </si>
+  <si>
+    <t>IF-07</t>
+  </si>
+  <si>
+    <t>ERP 연동</t>
+  </si>
+  <si>
+    <t>사용 부품 → ERP 차감</t>
+  </si>
+  <si>
+    <t>IT-IF-002</t>
+  </si>
+  <si>
+    <t>사용 부품 저장 후 Queueable이 ERP Mock에 차감을 보내고 결과·남은 수량을 기록하는지 확인</t>
+  </si>
+  <si>
+    <t>• Named Credential HG_ErpMock · 기사 보안 주체 접근</t>
+  </si>
+  <si>
+    <t>• IT-WO-002의 사용 부품</t>
+  </si>
+  <si>
+    <t>• ErpSyncStatus__c = Synced, ERP 남은 수량 기록</t>
+  </si>
+  <si>
+    <t>2026-10-13 실제 연동 확인, 최민호 사용 부품 3건 Synced(조회)</t>
+  </si>
+  <si>
+    <t>실패 건 재전송</t>
+  </si>
+  <si>
+    <t>IT-IF-003</t>
+  </si>
+  <si>
+    <t>ERP 장애로 실패한 전송을 매시 재전송 Batch가 다시 보내는지 확인</t>
+  </si>
+  <si>
+    <t>• ERP Mock 장애 모드(503)</t>
+  </si>
+  <si>
+    <t>• 장애 중 저장 → 장애 해제 → 재전송 실행</t>
+  </si>
+  <si>
+    <t>• Failed → Synced</t>
+  </si>
+  <si>
+    <t>2026-10-13 수동 재전송 실행 확인(decision-log ERP 12·13). 연동 전 대기 건 이중 차감 사고 기록 있음</t>
+  </si>
+  <si>
+    <t>사고 기록: decision-log ERP 13</t>
+  </si>
+  <si>
+    <t>ERP 재고 변동 푸시</t>
+  </si>
+  <si>
+    <t>IT-IF-004</t>
+  </si>
+  <si>
+    <t>ERP Mock에서 입고·조정하면 즉시 Salesforce 재고에 변동량만큼 반영되는지 확인</t>
+  </si>
+  <si>
+    <t>• 외부 클라이언트 앱 · 연동 사용자 권한 2개</t>
+  </si>
+  <si>
+    <t>• ERP Mock 입고 +1, 조정 −5</t>
+  </si>
+  <si>
+    <t>• 화면 "즉시 반영됨", 재고 19 → 20 → 15</t>
+  </si>
+  <si>
+    <t>2026-10-15: #47 입고 +1·#48 조정 −5 즉시 반영, ERP 기록 "· 푸시"(작성자 ERP 연동). 첫 호출은 공유·권한 결함 2건 → 수정 후 성공</t>
+  </si>
+  <si>
+    <t>IF-02-P</t>
+  </si>
+  <si>
+    <t>ERP 재고 변동 가져오기(안전망)</t>
+  </si>
+  <si>
+    <t>IT-IF-005</t>
+  </si>
+  <si>
+    <t>푸시로 이미 반영된 변동은 가져오기에서 중복으로 건너뛰고 기준 번호만 올리는지 확인</t>
+  </si>
+  <si>
+    <t>• IT-IF-004 이어서</t>
+  </si>
+  <si>
+    <t>• 가져오기 수동 실행</t>
+  </si>
+  <si>
+    <t>• 중복 2건 건너뜀, 기준 번호 46 → 48</t>
+  </si>
+  <si>
+    <t>2026-10-15: 중복 2건 건너뜀, 기준 번호 46 → 48, #43~#46은 가져오기로 반영</t>
+  </si>
+  <si>
+    <t>IF-02-R</t>
+  </si>
+  <si>
+    <t>재고 이동 수령 → ERP</t>
+  </si>
+  <si>
+    <t>IT-IF-006</t>
+  </si>
+  <si>
+    <t>창고 → 기사 차량 재고 이동을 기사가 수령하면 ERP로 이동이 전송되는지 확인</t>
+  </si>
+  <si>
+    <t>• 경기남부 창고 재고 · 최민호 차량</t>
+  </si>
+  <si>
+    <t>• 재고 이동 생성 → 수령</t>
+  </si>
+  <si>
+    <t>• ErpSyncStatus__c = Synced, Salesforce·ERP 재고 일치</t>
+  </si>
+  <si>
+    <t>2026-10-16: PT-0005 최민호가 창고 PI-0035(냉매 R-404A)에서 1kg 수령 → Salesforce·ERP 모두 창고 50→49 · 차량 13.5→14.5, ERP 완료·불일치 없음</t>
+  </si>
+  <si>
+    <t>IF-06</t>
+  </si>
+  <si>
+    <t>ERP Mock 입고 푸시 화면 확인</t>
+  </si>
+  <si>
+    <t>IT-IF-007</t>
+  </si>
+  <si>
+    <t>ERP Mock 재고 화면에서 입고하면 화면에 Salesforce 반영 결과가 바로 보이고, Salesforce 동기화 기록에 푸시로 남는지 확인</t>
+  </si>
+  <si>
+    <t>• ERP Mock 재고 화면(/)
+• 경기남부 창고 재고</t>
+  </si>
+  <si>
+    <t>• 입고 +1 → 결과 확인 → 조정 −1로 되돌림</t>
+  </si>
+  <si>
+    <t>• 화면 "즉시 반영됨", Salesforce 창고 +1, 동기화 기록 "· 푸시"</t>
+  </si>
+  <si>
+    <t>2026-10-18: 입고 +1 → "즉시 반영됨" → Salesforce 창고 +1, 동기화 기록 "· 푸시", 조정 −1로 되돌림(Edwin 화면 확인)</t>
+  </si>
+  <si>
+    <t>단위 테스트 (재검증)</t>
+  </si>
+  <si>
+    <t>전화 접수 · 조회 화면 (상담원 · 역할별 홈)</t>
+  </si>
+  <si>
+    <t>배정 · 출동 · 재고 (센터장 · 기사)</t>
+  </si>
+  <si>
+    <t>출동 승인 (기사 · 센터장)</t>
+  </si>
+  <si>
+    <t>외부 연동 (ERP · 주소)</t>
+  </si>
+  <si>
+    <t>I/F 테스트 결과 매트릭스</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 I/F별 테스트 케이스 수와 Pass/Fail을 [통합테스트 시나리오] 시트의 I/F 열(P)로 자동 집계합니다. 미실행은 Pass·Fail 어느 쪽에도 넣지 않습니다.</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>재고 변동 푸시</t>
+  </si>
+  <si>
+    <t>REST (Apex REST, OAuth)</t>
+  </si>
+  <si>
+    <t>ERP → SFDC</t>
+  </si>
+  <si>
+    <t>재고 변동 가져오기</t>
+  </si>
+  <si>
+    <t>REST (Batch)</t>
+  </si>
+  <si>
+    <t>사용 부품 차감</t>
+  </si>
+  <si>
+    <t>REST (Queueable)</t>
+  </si>
+  <si>
+    <t>SFDC → ERP</t>
+  </si>
+  <si>
+    <t>재고 이동</t>
+  </si>
+  <si>
+    <t>REST (form → JSON)</t>
+  </si>
+  <si>
+    <t>SFDC → 주소 API</t>
+  </si>
+  <si>
+    <t>IF-02-P 재고 변동 푸시</t>
+  </si>
+  <si>
+    <t>ERP Mock 입고·조정 직후 Apex REST(/services/apexrest/hg/erp/movements) 호출 → 재고 변동량 반영</t>
+  </si>
+  <si>
+    <t>IF-02-R 재고 변동 가져오기</t>
+  </si>
+  <si>
+    <t>매시 30분 Batch가 ERP 이력 번호 이후만 조회, 이미 기록된 번호는 건너뜀</t>
+  </si>
+  <si>
+    <t>IF-03 사용 부품 차감</t>
+  </si>
+  <si>
+    <t>사용 부품 저장 → Queueable → ERP 차감, 실패는 매시 재전송</t>
+  </si>
+  <si>
+    <t>IF-06 재고 이동</t>
+  </si>
+  <si>
+    <t>재고 이동 수령 → Queueable → ERP 출발 차감·도착 증가</t>
+  </si>
+  <si>
+    <t>IF-07 도로명주소 검색</t>
+  </si>
+  <si>
+    <t>사업장·고객사 주소 검색 → 행정안전부 API, 사업장 센터 자동 지정</t>
+  </si>
+  <si>
+    <t>한결공조 AS 관리 시스템 — 통합 테스트 결과 요약</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-11 ~ 2026-10-18 (개발 org, 실제 사용자 Login As + org 기록)</t>
+  </si>
+  <si>
+    <t>단위 테스트 (재검증)</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>전화 접수 · 조회 화면 (상담원 · 역할별 홈)</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>배정 · 출동 · 재고 (센터장 · 기사)</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>출동 승인 (기사 · 센터장)</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>외부 연동 (ERP · 주소)</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>유형</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행 중</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 · 검토</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>합계</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>한결공조 AS 관리 시스템</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>v1.1</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정 사항 목록 (단위 테스트 = 개발·테스트 중 발견, 통합 테스트 (1차) = 실제 사용자·실제 호출에서 발견)</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>접수·사용 부품(전체 화면)</t>
+  </si>
+  <si>
+    <t>API 67.0 기본 user mode로 상담원 접수 시 장비 집계 저장 안 됨, 기사 사용 부품 저장 불가 → 조회·DML 접근 모드 명시(시스템 계산 SYSTEM_MODE)</t>
+  </si>
+  <si>
+    <t>D6, 상담원·기사 runAs 테스트 추가 중 발견</t>
+  </si>
+  <si>
+    <t>출동 사용 부품(ERP 전송)</t>
+  </si>
+  <si>
+    <t>기사가 저장한 부품이 ERP로 전송되지 않음 → 외부 자격 증명 권한 집합 4개에 UserExternalCredential 읽기 추가</t>
+  </si>
+  <si>
+    <t>Login As 최민호(PC-245)</t>
+  </si>
+  <si>
+    <t>사업장 등록</t>
+  </si>
+  <si>
+    <t>상담원이 사업장을 등록하지 못함(서비스센터 편집 권한 없음) → 트리거가 주소 매핑으로 센터 지정</t>
+  </si>
+  <si>
+    <t>센터 완전 자동(decision-log 도로명주소 9)</t>
+  </si>
+  <si>
+    <t>차량 재고보다 많은 수량 입력 가능 → 화면·컨트롤러·트리거(VanStockService)에서 거부</t>
+  </si>
+  <si>
+    <t>보안 R1</t>
+  </si>
+  <si>
+    <t>고객사·사업장 등록</t>
+  </si>
+  <si>
+    <t>"새로 만들기"를 다시 누르면 이전 입력값이 남음(재정의 화면 캐시) → pageReference 변경 시 다시 그림</t>
+  </si>
+  <si>
+    <t>커밋 6e68ed4</t>
+  </si>
+  <si>
+    <t>주소 검색칸 Enter가 등록 화면 저장으로 이어짐 → Enter = 바로 검색</t>
+  </si>
+  <si>
+    <t>ERP Mock 재고 화면</t>
+  </si>
+  <si>
+    <t>입고·조정 입력에 API 키가 브라우저 화면에 필요했음 → 화면 전용 주소(키 없음)로 분리</t>
+  </si>
+  <si>
+    <t>부품 추가의 차량 재고 목록을 고를 수 없음(option에 disabled="false" 남음) → false 대신 null</t>
+  </si>
+  <si>
+    <t>커밋 375728a</t>
+  </si>
+  <si>
+    <t>ERP 푸시(IF-02-P)</t>
+  </si>
+  <si>
+    <t>연동 사용자 호출에서 위치를 못 찾음(SYSTEM_MODE도 공유는 클래스 선언을 따름) → 입구 without sharing</t>
+  </si>
+  <si>
+    <t>커밋 f3290d9, 테스트 normalAppliedByUserWithoutRecordAccess</t>
+  </si>
+  <si>
+    <t>연동 사용자가 재고 저장 불가(FIELD_INTEGRITY_EXCEPTION) → 재고·위치·제품 읽기 권한 집합 추가</t>
+  </si>
+  <si>
+    <t>HG_ErpIntegrationData</t>
+  </si>
+  <si>
+    <t>협력 기사 화면에 [승인 요청] 빠른 작업이 보이지 않음 → 원인: 출동 피드 추적이 켜져 빠른 작업이 Chatter 게시자 영역에 배치됐는데 출동 레코드 페이지에 피드 구성 요소가 없음. 강조 표시 패널을 동적 작업으로 전환(편집·승인 요청·소유자 변경·복제·삭제)</t>
+  </si>
+  <si>
+    <t>처음 추정(Flow 실행 권한)은 원인 아님. 최민호 화면 확인</t>
+  </si>
+  <si>
+    <t>사용 부품 삭제</t>
+  </si>
+  <si>
+    <t>삭제 시 표준과 Apex가 모두 재고를 되돌려 이중 증가(R6) → Apex 되돌림 제거, 테스트 기대값 수정(한 트랜잭션에선 표준 되돌림 없음), org에서 표준 1회 되돌림 확인(14.5→13.5→14.5)</t>
+  </si>
+  <si>
+    <t>decision-log ERP 19</t>
+  </si>
+  <si>
+    <t>출동 생성(표준 새로 만들기)</t>
+  </si>
+  <si>
+    <t>접수 없이 만든 출동의 서비스센터가 비어 센터장 공유 규칙이 걸리지 않음(5건) → 저장 전 Flow 안전망(접수 값 복사) + 기존 출동 채움, 출동 생성은 [기사 배정]으로 일원화</t>
+  </si>
+  <si>
+    <t>채운 뒤 센터장 역할 공유 생성 확인</t>
+  </si>
+  <si>
+    <t>출동 탭 앱 내 안내</t>
+  </si>
+  <si>
+    <t>안내 팝업이 아무에게도 뜨지 않음(대상 페이지 home, 출동 탭은 목록 list로 열림) → list로 수정(이후 게시 해제 결정)</t>
+  </si>
+  <si>
+    <t>표시 기록 0건으로 발견</t>
+  </si>
+  <si>
+    <t>재고 공유 규칙</t>
+  </si>
+  <si>
+    <t>다른 센터 창고 재고가 경기남부 기사·센터장에게 보임(소유자 기준 규칙: 관리자 소유 재고 전부) → 재고 서비스센터·창고 재고 필드 + 조건 기준 규칙</t>
+  </si>
+  <si>
+    <t>검증용 서울 창고 레코드로 발견, 테스트 ProductItemLocationFlowTest</t>
+  </si>
+  <si>
+    <t>기사 배정 출동 출장비</t>
+  </si>
+  <si>
+    <t>[기사 배정] 출동에 출장비가 비어 청구 합계에서 빠짐 → DispatchService 출장비 = ServiceSetting VisitFee, 저장 전 Flow 안전망</t>
+  </si>
+  <si>
+    <t>한 사이클 실습 중 발견(00000049)</t>
+  </si>
+  <si>
+    <t>승인 요청 요약</t>
+  </si>
+  <si>
+    <t>Flow 텍스트 템플릿 앞뒤 줄바꿈이 지워져 요약 줄이 붙음 → 줄바꿈을 템플릿 가운데에 둠</t>
+  </si>
+  <si>
+    <t>WorkOrderApprovalFlowTest로 발견</t>
+  </si>
+  <si>
+    <t>접수 완료 검증 규칙 테스트</t>
+  </si>
+  <si>
+    <t>관리자(검증 우회 권한)로 실행한 테스트에서 BR-18 규칙이 동작하지 않음 → 상담원 사용자로 runAs</t>
+  </si>
+  <si>
+    <t>CaseWorkOrderStatsServiceTest</t>
+  </si>
+  <si>
+    <t>개발 도구(커밋 훅)</t>
+  </si>
+  <si>
+    <t>Prettier가 권한 집합 &lt;flow&gt; 값을 JS로 포맷해 망가뜨림 → XML 내장 언어 포맷 끔</t>
+  </si>
+  <si>
+    <t>커밋 22c613a</t>
+  </si>
+  <si>
+    <t>한결공조 AS 관리 시스템 — 테스트 결과서 요약</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>※ [수정사항관리] 시트 기준 / 단위 테스트 · 통합 테스트(1차) 결과 요약. 2차·오픈 전 테스트는 이번 범위(개발 org)에서 실시하지 않음</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발·테스트 중 발견 결함 11건 모두 완료(R6 반영 2026-10-16). 단위 테스트 248건 Pass(07 V1.1)</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>미실시</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>샌드박스 배포 후 실시 예정</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>운영 배포 전 실시 예정</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-18 시연 연습 [시연/재고 부족]: 최민호가 배수펌프 DP-4 2개 추가 → "남은 1개" 거부 → 재고 이동(경기남부 창고 → 차량 2) 수령, ERP 반영 → 다시 2개 추가 성공, Salesforce·ERP 모두 차감(Edwin 화면 확인)</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>• "차량 재고가 부족합니다" 거부 → 보충 후 저장</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>• 수량 2 입력 → 재고 이동(창고 → 차량) 수령 → 다시 2 입력</t>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>• 최민호(기사) 로그인
 • [시연/재고 부족] 출동(차량 배수펌프 DP-4 1개)</t>
-  </si>
-  <si>
-    <t>• 수량 2 입력 → 재고 이동(창고 → 차량) 수령 → 다시 2 입력</t>
-  </si>
-  <si>
-    <t>• "차량 재고가 부족합니다" 거부 → 보충 후 저장</t>
-  </si>
-  <si>
-    <t>연습 예정 (2026-10-18 시연 연습 [시연/재고 부족]으로 확인 후 기입. Apex 테스트 VanStockService·WorkOrderPartsController는 Pass)</t>
-  </si>
-  <si>
-    <t>연습 예정</t>
-  </si>
-  <si>
-    <t>한 사이클</t>
-  </si>
-  <si>
-    <t>접수 → 배정 → 부품 → 완료 → 종결</t>
-  </si>
-  <si>
-    <t>IT-WO-004</t>
-  </si>
-  <si>
-    <t>상담원 접수부터 종결까지 세 사용자가 실제 화면으로 한 번에 처리되는지 확인</t>
-  </si>
-  <si>
-    <t>• 이서연·김병철·최민호 로그인</t>
-  </si>
-  <si>
-    <t>• 가상 착신 010-1111-2002 → 중복 경고 00001028 [기존 접수 열기] → 김병철 [기사 배정] → 최민호 수락·도착·부품 → 완료 → 종결</t>
-  </si>
-  <si>
-    <t>• 새 접수 없이 기존 접수로 처리, 출동 생성·부품 ERP 전송·승인 불필요 안내, 종결 후 수정 잠김</t>
-  </si>
-  <si>
-    <t>2026-10-16: 00001028 → 출동 00000049 → 냉매 R-404A 0.5kg(차량 14.5→14.0, ERP 완료) → 승인 불필요 안내(₩20,000 / 기준 ₩500,000) → 출동 완료 → 접수 완료 → 종결 → 수정 시 잠김 경고. 실습 중 결함 1건(출장비 빈칸) 수정</t>
-  </si>
-  <si>
-    <t>접수 자동 완료</t>
-  </si>
-  <si>
-    <t>접수 자동 완료 · 종결 대기 · BR-18</t>
-  </si>
-  <si>
-    <t>IT-WO-005</t>
-  </si>
-  <si>
-    <t>마지막 열린 출동이 완료되면 접수가 자동 완료되고 센터장 "종결 대기 접수"에 보이며, 열린 출동이 있으면 완료·종결할 수 없는지 확인</t>
-  </si>
-  <si>
-    <t>• 처리 중 접수 + 출동 1건</t>
-  </si>
-  <si>
-    <t>• 출동 완료 → 센터장 홈 확인</t>
-  </si>
-  <si>
-    <t>• 접수 완료(열린 0·완료 1), 종결 대기 목록 표시, 열린 출동이 있으면 완료·종결 거부</t>
-  </si>
-  <si>
-    <t>2026-10-18 시연 준비: 출동 00000064·00000065 완료 → 접수 00001996·00001997 자동 완료(열린 0·완료 1), 종결 대기 3건(조회). 리셋 검증: 종결 → 완료 복원. 열린 출동 거부는 Apex 테스트 CaseWorkOrderStatsServiceTest(상담원 runAs) Pass</t>
-  </si>
-  <si>
-    <t>재고 공유</t>
-  </si>
-  <si>
-    <t>다른 센터 창고 재고 비공개</t>
-  </si>
-  <si>
-    <t>IT-WO-006</t>
-  </si>
-  <si>
-    <t>경기남부 기사·센터장은 경기남부 창고 재고만 읽고 다른 센터(서울) 창고 재고는 못 보는지 확인</t>
-  </si>
-  <si>
-    <t>• 검증용 서울 창고 위치·재고 1건(조회 후 삭제)
-• 조건 기준 공유 규칙 HG_GyeonggiSouth_Warehouse_Stock_Tech</t>
-  </si>
-  <si>
-    <t>• UserRecordAccess(HasReadAccess) × 김병철·최민호·이서연</t>
-  </si>
-  <si>
-    <t>• 서울 창고 재고: 김병철·최민호 읽기 없음 / 경기남부 창고 재고 14건 읽기 유지</t>
-  </si>
-  <si>
-    <t>2026-10-16: 규칙 교체 전 결함(서울 창고 재고 읽기) 발견 → 조건 기준 규칙으로 교체 후 서울 창고 재고 김병철·최민호 읽기 없음, 경기남부 창고 재고 14건 유지, 상담원 전체 읽기 유지</t>
-  </si>
-  <si>
-    <t>결함 이력: 수정사항관리 · 재고 이동 공유 없음은 한계</t>
-  </si>
-  <si>
-    <t>PROCESS 3 · 출동 승인 (기사 · 센터장)</t>
-  </si>
-  <si>
-    <t>출동 승인 요청</t>
-  </si>
-  <si>
-    <t>승인 불필요 출동 안내</t>
-  </si>
-  <si>
-    <t>IT-APV-001</t>
-  </si>
-  <si>
-    <t>예외 무상이 없고 청구 합계가 기준 이하인 출동에서 [승인 요청]을 누르면 안내만 나오는지 확인</t>
-  </si>
-  <si>
-    <t>• 출동 00000038(500,000)·00000039(30,000)</t>
-  </si>
-  <si>
-    <t>• 빠른 작업 [승인 요청]</t>
-  </si>
-  <si>
-    <t>• "승인이 필요하지 않습니다" 안내</t>
-  </si>
-  <si>
-    <t>2026-10-16: 최민호 화면에서 "승인이 필요하지 않습니다" 안내 확인(Edwin)</t>
-  </si>
-  <si>
-    <t>기사 승인 요청 제출</t>
-  </si>
-  <si>
-    <t>IT-APV-002</t>
-  </si>
-  <si>
-    <t>기준 초과 출동에서 기사가 사유·고객 동의를 넣어 승인 요청 → 센터장에게 승인 요청이 가는지 확인</t>
-  </si>
-  <si>
-    <t>• 최민호(기사) · Manager = 김병철
-• 출동 00000037 청구 합계 1,200,000</t>
-  </si>
-  <si>
-    <t>• 사유 "고객 과실" · 고객 동의 체크</t>
-  </si>
-  <si>
-    <t>• 상태 승인 대기, 승인자 김병철</t>
-  </si>
-  <si>
-    <t>2026-10-15 17:46: 최민호 제출(사유 "고객 과실", 고객 동의 저장), 승인자 김병철 — org 승인 기록. 출동의 [승인 요청] 빠른 작업으로 제출(Edwin)</t>
-  </si>
-  <si>
-    <t>출동 승인</t>
-  </si>
-  <si>
-    <t>센터장 승인</t>
-  </si>
-  <si>
-    <t>IT-APV-003</t>
-  </si>
-  <si>
-    <t>센터장이 승인하면 출동이 도착 상태로 돌아오고 승인 상태가 승인으로 바뀌는지 확인</t>
-  </si>
-  <si>
-    <t>• IT-APV-002 이어서 · 김병철 로그인</t>
-  </si>
-  <si>
-    <t>• 승인 요청 → [승인]</t>
-  </si>
-  <si>
-    <t>• 승인 상태 Approved · 상태 Arrived</t>
-  </si>
-  <si>
-    <t>2026-10-15 17:47: 김병철 승인, 출동 00000037 승인 상태 Approved · 상태 Arrived(조회 확인)</t>
-  </si>
-  <si>
-    <t>반려 시 사유 필수 · 도착 복귀</t>
-  </si>
-  <si>
-    <t>IT-APV-004</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>남은 수량보다 많이 입력하면 저장이 거부되고 재고 이동으로 보충한 뒤에는 저장되는지 확인</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>유상 전환: 2026-10-18 시연 연습에서 확인(Edwin)</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pass</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-11: 출동 00000001 반려 기록(org 승인 기록). 2026-10-18 시연 연습 [시연/승인 반려]: 김병철 거부 후 예외 무상 부품이 유상으로 전환(HG_WO_AfterReject) 확인</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>• 상태 Arrived, 예외 무상은 유상 전환</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>• [반려] + 반려 사유</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>• 승인 대기 출동</t>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>센터장이 반려하면 반려 사유가 필수이고 출동이 도착으로 돌아오는지 확인</t>
-  </si>
-  <si>
-    <t>• 승인 대기 출동</t>
-  </si>
-  <si>
-    <t>• [반려] + 반려 사유</t>
-  </si>
-  <si>
-    <t>• 상태 Arrived, 예외 무상은 유상 전환</t>
-  </si>
-  <si>
-    <t>2026-10-11: 출동 00000001 반려 기록(org 승인 기록). 예외 무상 → 유상 전환은 시연 [시연/승인 반려]로 재확인 예정</t>
-  </si>
-  <si>
-    <t>유상 전환 재확인: 시연 연습</t>
-  </si>
-  <si>
-    <t>기사 화면 [승인 요청] 표시</t>
-  </si>
-  <si>
-    <t>IT-APV-005</t>
-  </si>
-  <si>
-    <t>협력 기사의 출동 화면 강조 패널에 빠른 작업 [승인 요청]이 보이는지 확인</t>
-  </si>
-  <si>
-    <t>• 출동 레코드 화면 열기</t>
-  </si>
-  <si>
-    <t>• [승인 요청] 버튼 표시</t>
-  </si>
-  <si>
-    <t>2026-10-15 버튼 미표시 → 원인: 출동 피드 추적으로 빠른 작업이 Chatter 게시자 영역에 배치(페이지에 피드 없음). 강조 표시 패널을 동적 작업으로 전환 후 최민호 화면에서 표시 확인. Flow 실행 권한은 추가하지 않음(개별 Flow 접근만으로 동작)</t>
-  </si>
-  <si>
-    <t>결함 수정 후 재확인</t>
-  </si>
-  <si>
-    <t>승인 요청 요약 · 승인할 항목</t>
-  </si>
-  <si>
-    <t>IT-APV-006</t>
-  </si>
-  <si>
-    <t>기사가 제출하면 승인 요청 요약(이유·부품별 줄·사유·고객 동의·메모)이 제출 댓글·출동 필드에 남고, 센터장 홈 "승인할 항목"과 승인 화면 필드 13개로 판단할 수 있는지 확인</t>
-  </si>
-  <si>
-    <t>• [테스트] 접수 00001980 · 출동 00000050(₩850,000)</t>
-  </si>
-  <si>
-    <t>• 최민호 [승인 요청] 제출 → 김병철 홈 "승인할 항목" → 승인 화면</t>
-  </si>
-  <si>
-    <t>• 승인할 항목에 00000050 표시, 승인 화면 필드 13개, 제출자 댓글 = 요약</t>
-  </si>
-  <si>
-    <t>2026-10-16: 김병철 홈 "승인할 항목"에 00000050 표시, 승인 화면 필드·제출자 댓글(요약) 확인 → 회수, 테스트 데이터(접수 00001980·출동 00000050·사용 부품 2) 삭제</t>
-  </si>
-  <si>
-    <t>결함 이력: 수정사항관리(요약 줄바꿈)</t>
-  </si>
-  <si>
-    <t>PROCESS 4 · 외부 연동 (ERP · 주소)</t>
-  </si>
-  <si>
-    <t>도로명주소 검색</t>
-  </si>
-  <si>
-    <t>주소 검색 실제 호출</t>
-  </si>
-  <si>
-    <t>IT-IF-001</t>
-  </si>
-  <si>
-    <t>사업장 빠른 작업 "주소 검색"이 도로명주소 API를 호출해 결과를 보여 주는지 확인</t>
-  </si>
-  <si>
-    <t>• 승인키(보안 주체 HG_JusoPrincipal) 입력됨</t>
-  </si>
-  <si>
-    <t>• 검색어 "평택로 32"</t>
-  </si>
-  <si>
-    <t>• 결과 목록 · 더 보기</t>
-  </si>
-  <si>
-    <t>2026-10-13 실제 호출 확인, 2026-10-15 "평택로 32" 24건 중 10건 표시(화면 캡처), 2026-10-18 이서연 화면 "판교역로 166" 결과 표시</t>
-  </si>
-  <si>
-    <t>IF-07</t>
-  </si>
-  <si>
-    <t>ERP 연동</t>
-  </si>
-  <si>
-    <t>사용 부품 → ERP 차감</t>
-  </si>
-  <si>
-    <t>IT-IF-002</t>
-  </si>
-  <si>
-    <t>사용 부품 저장 후 Queueable이 ERP Mock에 차감을 보내고 결과·남은 수량을 기록하는지 확인</t>
-  </si>
-  <si>
-    <t>• Named Credential HG_ErpMock · 기사 보안 주체 접근</t>
-  </si>
-  <si>
-    <t>• IT-WO-002의 사용 부품</t>
-  </si>
-  <si>
-    <t>• ErpSyncStatus__c = Synced, ERP 남은 수량 기록</t>
-  </si>
-  <si>
-    <t>2026-10-13 실제 연동 확인, 최민호 사용 부품 3건 Synced(조회)</t>
-  </si>
-  <si>
-    <t>실패 건 재전송</t>
-  </si>
-  <si>
-    <t>IT-IF-003</t>
-  </si>
-  <si>
-    <t>ERP 장애로 실패한 전송을 매시 재전송 Batch가 다시 보내는지 확인</t>
-  </si>
-  <si>
-    <t>• ERP Mock 장애 모드(503)</t>
-  </si>
-  <si>
-    <t>• 장애 중 저장 → 장애 해제 → 재전송 실행</t>
-  </si>
-  <si>
-    <t>• Failed → Synced</t>
-  </si>
-  <si>
-    <t>2026-10-13 수동 재전송 실행 확인(decision-log ERP 12·13). 연동 전 대기 건 이중 차감 사고 기록 있음</t>
-  </si>
-  <si>
-    <t>사고 기록: decision-log ERP 13</t>
-  </si>
-  <si>
-    <t>ERP 재고 변동 푸시</t>
-  </si>
-  <si>
-    <t>IT-IF-004</t>
-  </si>
-  <si>
-    <t>ERP Mock에서 입고·조정하면 즉시 Salesforce 재고에 변동량만큼 반영되는지 확인</t>
-  </si>
-  <si>
-    <t>• 외부 클라이언트 앱 · 연동 사용자 권한 2개</t>
-  </si>
-  <si>
-    <t>• ERP Mock 입고 +1, 조정 −5</t>
-  </si>
-  <si>
-    <t>• 화면 "즉시 반영됨", 재고 19 → 20 → 15</t>
-  </si>
-  <si>
-    <t>2026-10-15: #47 입고 +1·#48 조정 −5 즉시 반영, ERP 기록 "· 푸시"(작성자 ERP 연동). 첫 호출은 공유·권한 결함 2건 → 수정 후 성공</t>
-  </si>
-  <si>
-    <t>IF-02-P</t>
-  </si>
-  <si>
-    <t>ERP 재고 변동 가져오기(안전망)</t>
-  </si>
-  <si>
-    <t>IT-IF-005</t>
-  </si>
-  <si>
-    <t>푸시로 이미 반영된 변동은 가져오기에서 중복으로 건너뛰고 기준 번호만 올리는지 확인</t>
-  </si>
-  <si>
-    <t>• IT-IF-004 이어서</t>
-  </si>
-  <si>
-    <t>• 가져오기 수동 실행</t>
-  </si>
-  <si>
-    <t>• 중복 2건 건너뜀, 기준 번호 46 → 48</t>
-  </si>
-  <si>
-    <t>2026-10-15: 중복 2건 건너뜀, 기준 번호 46 → 48, #43~#46은 가져오기로 반영</t>
-  </si>
-  <si>
-    <t>IF-02-R</t>
-  </si>
-  <si>
-    <t>재고 이동 수령 → ERP</t>
-  </si>
-  <si>
-    <t>IT-IF-006</t>
-  </si>
-  <si>
-    <t>창고 → 기사 차량 재고 이동을 기사가 수령하면 ERP로 이동이 전송되는지 확인</t>
-  </si>
-  <si>
-    <t>• 경기남부 창고 재고 · 최민호 차량</t>
-  </si>
-  <si>
-    <t>• 재고 이동 생성 → 수령</t>
-  </si>
-  <si>
-    <t>• ErpSyncStatus__c = Synced, Salesforce·ERP 재고 일치</t>
-  </si>
-  <si>
-    <t>2026-10-16: PT-0005 최민호가 창고 PI-0035(냉매 R-404A)에서 1kg 수령 → Salesforce·ERP 모두 창고 50→49 · 차량 13.5→14.5, ERP 완료·불일치 없음</t>
-  </si>
-  <si>
-    <t>IF-06</t>
-  </si>
-  <si>
-    <t>ERP Mock 입고 푸시 화면 확인</t>
-  </si>
-  <si>
-    <t>IT-IF-007</t>
-  </si>
-  <si>
-    <t>ERP Mock 재고 화면에서 입고하면 화면에 Salesforce 반영 결과가 바로 보이고, Salesforce 동기화 기록에 푸시로 남는지 확인</t>
-  </si>
-  <si>
-    <t>• ERP Mock 재고 화면(/)
-• 경기남부 창고 재고</t>
-  </si>
-  <si>
-    <t>• 입고 +1 → 결과 확인 → 조정 −1로 되돌림</t>
-  </si>
-  <si>
-    <t>• 화면 "즉시 반영됨", Salesforce 창고 +1, 동기화 기록 "· 푸시"</t>
-  </si>
-  <si>
-    <t>2026-10-18: 입고 +1 → "즉시 반영됨" → Salesforce 창고 +1, 동기화 기록 "· 푸시", 조정 −1로 되돌림(Edwin 화면 확인)</t>
-  </si>
-  <si>
-    <t>단위 테스트 (재검증)</t>
-  </si>
-  <si>
-    <t>전화 접수 · 조회 화면 (상담원 · 역할별 홈)</t>
-  </si>
-  <si>
-    <t>배정 · 출동 · 재고 (센터장 · 기사)</t>
-  </si>
-  <si>
-    <t>출동 승인 (기사 · 센터장)</t>
-  </si>
-  <si>
-    <t>외부 연동 (ERP · 주소)</t>
-  </si>
-  <si>
-    <t>I/F 테스트 결과 매트릭스</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>각 I/F별 테스트 케이스 수와 Pass/Fail을 [통합테스트 시나리오] 시트의 I/F 열(P)로 자동 집계합니다. 미실행은 Pass·Fail 어느 쪽에도 넣지 않습니다.</t>
+    <t>실제 사용자·실제 호출에서 발견한 결함 8건 모두 완료. 시나리오 27건: Pass 27 · 미실행 0</t>
     <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>재고 변동 푸시</t>
-  </si>
-  <si>
-    <t>REST (Apex REST, OAuth)</t>
-  </si>
-  <si>
-    <t>ERP → SFDC</t>
-  </si>
-  <si>
-    <t>재고 변동 가져오기</t>
-  </si>
-  <si>
-    <t>REST (Batch)</t>
-  </si>
-  <si>
-    <t>사용 부품 차감</t>
-  </si>
-  <si>
-    <t>REST (Queueable)</t>
-  </si>
-  <si>
-    <t>SFDC → ERP</t>
-  </si>
-  <si>
-    <t>재고 이동</t>
-  </si>
-  <si>
-    <t>REST (form → JSON)</t>
-  </si>
-  <si>
-    <t>SFDC → 주소 API</t>
-  </si>
-  <si>
-    <t>IF-02-P 재고 변동 푸시</t>
-  </si>
-  <si>
-    <t>ERP Mock 입고·조정 직후 Apex REST(/services/apexrest/hg/erp/movements) 호출 → 재고 변동량 반영</t>
-  </si>
-  <si>
-    <t>IF-02-R 재고 변동 가져오기</t>
-  </si>
-  <si>
-    <t>매시 30분 Batch가 ERP 이력 번호 이후만 조회, 이미 기록된 번호는 건너뜀</t>
-  </si>
-  <si>
-    <t>IF-03 사용 부품 차감</t>
-  </si>
-  <si>
-    <t>사용 부품 저장 → Queueable → ERP 차감, 실패는 매시 재전송</t>
-  </si>
-  <si>
-    <t>IF-06 재고 이동</t>
-  </si>
-  <si>
-    <t>재고 이동 수령 → Queueable → ERP 출발 차감·도착 증가</t>
-  </si>
-  <si>
-    <t>IF-07 도로명주소 검색</t>
-  </si>
-  <si>
-    <t>사업장·고객사 주소 검색 → 행정안전부 API, 사업장 센터 자동 지정</t>
-  </si>
-  <si>
-    <t>한결공조 AS 관리 시스템 — 통합 테스트 결과 요약</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026-10-11 ~ 2026-10-18 (개발 org, 실제 사용자 Login As + org 기록)</t>
-  </si>
-  <si>
-    <t>단위 테스트 (재검증)</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>전화 접수 · 조회 화면 (상담원 · 역할별 홈)</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>배정 · 출동 · 재고 (센터장 · 기사)</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>출동 승인 (기사 · 센터장)</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>외부 연동 (ERP · 주소)</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>유형</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>진행 중</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 · 검토</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>합계</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>한결공조 AS 관리 시스템</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>v1.1</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>수정 사항 목록 (단위 테스트 = 개발·테스트 중 발견, 통합 테스트 (1차) = 실제 사용자·실제 호출에서 발견)</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>접수·사용 부품(전체 화면)</t>
-  </si>
-  <si>
-    <t>API 67.0 기본 user mode로 상담원 접수 시 장비 집계 저장 안 됨, 기사 사용 부품 저장 불가 → 조회·DML 접근 모드 명시(시스템 계산 SYSTEM_MODE)</t>
-  </si>
-  <si>
-    <t>D6, 상담원·기사 runAs 테스트 추가 중 발견</t>
-  </si>
-  <si>
-    <t>출동 사용 부품(ERP 전송)</t>
-  </si>
-  <si>
-    <t>기사가 저장한 부품이 ERP로 전송되지 않음 → 외부 자격 증명 권한 집합 4개에 UserExternalCredential 읽기 추가</t>
-  </si>
-  <si>
-    <t>Login As 최민호(PC-245)</t>
-  </si>
-  <si>
-    <t>사업장 등록</t>
-  </si>
-  <si>
-    <t>상담원이 사업장을 등록하지 못함(서비스센터 편집 권한 없음) → 트리거가 주소 매핑으로 센터 지정</t>
-  </si>
-  <si>
-    <t>센터 완전 자동(decision-log 도로명주소 9)</t>
-  </si>
-  <si>
-    <t>차량 재고보다 많은 수량 입력 가능 → 화면·컨트롤러·트리거(VanStockService)에서 거부</t>
-  </si>
-  <si>
-    <t>보안 R1</t>
-  </si>
-  <si>
-    <t>고객사·사업장 등록</t>
-  </si>
-  <si>
-    <t>"새로 만들기"를 다시 누르면 이전 입력값이 남음(재정의 화면 캐시) → pageReference 변경 시 다시 그림</t>
-  </si>
-  <si>
-    <t>커밋 6e68ed4</t>
-  </si>
-  <si>
-    <t>주소 검색칸 Enter가 등록 화면 저장으로 이어짐 → Enter = 바로 검색</t>
-  </si>
-  <si>
-    <t>ERP Mock 재고 화면</t>
-  </si>
-  <si>
-    <t>입고·조정 입력에 API 키가 브라우저 화면에 필요했음 → 화면 전용 주소(키 없음)로 분리</t>
-  </si>
-  <si>
-    <t>부품 추가의 차량 재고 목록을 고를 수 없음(option에 disabled="false" 남음) → false 대신 null</t>
-  </si>
-  <si>
-    <t>커밋 375728a</t>
-  </si>
-  <si>
-    <t>ERP 푸시(IF-02-P)</t>
-  </si>
-  <si>
-    <t>연동 사용자 호출에서 위치를 못 찾음(SYSTEM_MODE도 공유는 클래스 선언을 따름) → 입구 without sharing</t>
-  </si>
-  <si>
-    <t>커밋 f3290d9, 테스트 normalAppliedByUserWithoutRecordAccess</t>
-  </si>
-  <si>
-    <t>연동 사용자가 재고 저장 불가(FIELD_INTEGRITY_EXCEPTION) → 재고·위치·제품 읽기 권한 집합 추가</t>
-  </si>
-  <si>
-    <t>HG_ErpIntegrationData</t>
-  </si>
-  <si>
-    <t>협력 기사 화면에 [승인 요청] 빠른 작업이 보이지 않음 → 원인: 출동 피드 추적이 켜져 빠른 작업이 Chatter 게시자 영역에 배치됐는데 출동 레코드 페이지에 피드 구성 요소가 없음. 강조 표시 패널을 동적 작업으로 전환(편집·승인 요청·소유자 변경·복제·삭제)</t>
-  </si>
-  <si>
-    <t>처음 추정(Flow 실행 권한)은 원인 아님. 최민호 화면 확인</t>
-  </si>
-  <si>
-    <t>사용 부품 삭제</t>
-  </si>
-  <si>
-    <t>삭제 시 표준과 Apex가 모두 재고를 되돌려 이중 증가(R6) → Apex 되돌림 제거, 테스트 기대값 수정(한 트랜잭션에선 표준 되돌림 없음), org에서 표준 1회 되돌림 확인(14.5→13.5→14.5)</t>
-  </si>
-  <si>
-    <t>decision-log ERP 19</t>
-  </si>
-  <si>
-    <t>출동 생성(표준 새로 만들기)</t>
-  </si>
-  <si>
-    <t>접수 없이 만든 출동의 서비스센터가 비어 센터장 공유 규칙이 걸리지 않음(5건) → 저장 전 Flow 안전망(접수 값 복사) + 기존 출동 채움, 출동 생성은 [기사 배정]으로 일원화</t>
-  </si>
-  <si>
-    <t>채운 뒤 센터장 역할 공유 생성 확인</t>
-  </si>
-  <si>
-    <t>출동 탭 앱 내 안내</t>
-  </si>
-  <si>
-    <t>안내 팝업이 아무에게도 뜨지 않음(대상 페이지 home, 출동 탭은 목록 list로 열림) → list로 수정(이후 게시 해제 결정)</t>
-  </si>
-  <si>
-    <t>표시 기록 0건으로 발견</t>
-  </si>
-  <si>
-    <t>재고 공유 규칙</t>
-  </si>
-  <si>
-    <t>다른 센터 창고 재고가 경기남부 기사·센터장에게 보임(소유자 기준 규칙: 관리자 소유 재고 전부) → 재고 서비스센터·창고 재고 필드 + 조건 기준 규칙</t>
-  </si>
-  <si>
-    <t>검증용 서울 창고 레코드로 발견, 테스트 ProductItemLocationFlowTest</t>
-  </si>
-  <si>
-    <t>기사 배정 출동 출장비</t>
-  </si>
-  <si>
-    <t>[기사 배정] 출동에 출장비가 비어 청구 합계에서 빠짐 → DispatchService 출장비 = ServiceSetting VisitFee, 저장 전 Flow 안전망</t>
-  </si>
-  <si>
-    <t>한 사이클 실습 중 발견(00000049)</t>
-  </si>
-  <si>
-    <t>승인 요청 요약</t>
-  </si>
-  <si>
-    <t>Flow 텍스트 템플릿 앞뒤 줄바꿈이 지워져 요약 줄이 붙음 → 줄바꿈을 템플릿 가운데에 둠</t>
-  </si>
-  <si>
-    <t>WorkOrderApprovalFlowTest로 발견</t>
-  </si>
-  <si>
-    <t>접수 완료 검증 규칙 테스트</t>
-  </si>
-  <si>
-    <t>관리자(검증 우회 권한)로 실행한 테스트에서 BR-18 규칙이 동작하지 않음 → 상담원 사용자로 runAs</t>
-  </si>
-  <si>
-    <t>CaseWorkOrderStatsServiceTest</t>
-  </si>
-  <si>
-    <t>개발 도구(커밋 훅)</t>
-  </si>
-  <si>
-    <t>Prettier가 권한 집합 &lt;flow&gt; 값을 JS로 포맷해 망가뜨림 → XML 내장 언어 포맷 끔</t>
-  </si>
-  <si>
-    <t>커밋 22c613a</t>
-  </si>
-  <si>
-    <t>한결공조 AS 관리 시스템 — 테스트 결과서 요약</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>※ [수정사항관리] 시트 기준 / 단위 테스트 · 통합 테스트(1차) 결과 요약. 2차·오픈 전 테스트는 이번 범위(개발 org)에서 실시하지 않음</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>개발·테스트 중 발견 결함 11건 모두 완료(R6 반영 2026-10-16). 단위 테스트 248건 Pass(07 V1.1)</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>실제 사용자·실제 호출에서 발견한 결함 8건 모두 완료. 시나리오 27건: Pass 26 · 연습 예정 1(재고 초과 화면, [시연/재고 부족])</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>미실시</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>샌드박스 배포 후 실시 예정</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>운영 배포 전 실시 예정</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>v1.1</t>
   </si>
 </sst>
 </file>
@@ -3084,6 +3093,15 @@
     <xf numFmtId="176" fontId="21" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3093,16 +3111,10 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3110,9 +3122,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3405,7 +3414,7 @@
   <sheetData>
     <row r="2" spans="2:9" ht="36" customHeight="1">
       <c r="B2" s="101" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="C2" s="100"/>
       <c r="D2" s="100"/>
@@ -3417,7 +3426,7 @@
     </row>
     <row r="3" spans="2:9" ht="22" customHeight="1">
       <c r="B3" s="102" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C3" s="100"/>
       <c r="D3" s="100"/>
@@ -3446,7 +3455,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="68" t="s">
-        <v>426</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="26.15" customHeight="1">
@@ -3514,10 +3523,10 @@
         <v>14</v>
       </c>
       <c r="I8" s="92" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="43.5">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="29">
       <c r="B9" s="66" t="s">
         <v>15</v>
       </c>
@@ -3544,7 +3553,7 @@
         <v>14</v>
       </c>
       <c r="I9" s="93" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="16">
@@ -3571,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="67" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="I10" s="93" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="16.5" thickBot="1">
@@ -3601,10 +3610,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="67" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="I11" s="93" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="17.5" thickBot="1">
@@ -3843,75 +3852,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1">
-      <c r="A1" s="110" t="s">
-        <v>355</v>
-      </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
+      <c r="A1" s="106" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1">
       <c r="A3" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="107" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
       <c r="E3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="111">
+      <c r="F3" s="108">
         <v>46313</v>
       </c>
-      <c r="G3" s="111"/>
+      <c r="G3" s="108"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
       <c r="A4" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="109" t="s">
-        <v>356</v>
-      </c>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
+      <c r="B4" s="107" t="s">
+        <v>344</v>
+      </c>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
       <c r="E4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="109" t="s">
+      <c r="F4" s="107" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="109"/>
+      <c r="G4" s="107"/>
     </row>
     <row r="5" spans="1:7" ht="16">
       <c r="A5" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="109" t="s">
+      <c r="B5" s="107" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
       <c r="E5" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
     </row>
     <row r="7" spans="1:7" ht="24" customHeight="1">
-      <c r="A7" s="106" t="s">
+      <c r="A7" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="106"/>
-      <c r="C7" s="106"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1">
       <c r="A8" s="1" t="s">
@@ -3943,7 +3952,7 @@
       </c>
       <c r="B9" s="27">
         <f>COUNTIF('통합테스트 시나리오'!$M$4:$M$272, "Pass")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="28">
         <f>COUNTIF('통합테스트 시나리오'!$M$4:$M$272, "Fail")</f>
@@ -3951,7 +3960,7 @@
       </c>
       <c r="D9" s="29">
         <f>A9-B9-C9</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="30">
         <f>IFERROR(B9/(B9+C9), 0)</f>
@@ -3959,23 +3968,23 @@
       </c>
       <c r="F9" s="30">
         <f>IFERROR((B9+C9)/A9, 0)</f>
-        <v>0.96296296296296291</v>
+        <v>1</v>
       </c>
       <c r="G9" s="31" t="str">
         <f>IF(F9&lt;1, "진행 중", IF(E9&gt;=0.95, "✓ Pass", IF(E9&gt;=0.8, "△ 조건부", "✗ Fail")))</f>
-        <v>진행 중</v>
+        <v>✓ Pass</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="24" customHeight="1">
-      <c r="A11" s="106" t="s">
+      <c r="A11" s="109" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="106"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
+      <c r="B11" s="109"/>
+      <c r="C11" s="109"/>
+      <c r="D11" s="109"/>
+      <c r="E11" s="109"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="109"/>
     </row>
     <row r="12" spans="1:7" ht="27.75" customHeight="1">
       <c r="A12" s="4" t="s">
@@ -4005,7 +4014,7 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="C13" s="33">
         <f>COUNTIF('통합테스트 시나리오'!$B$4:$B$272, "0")</f>
@@ -4033,7 +4042,7 @@
         <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="C14" s="33">
         <f>COUNTIF('통합테스트 시나리오'!$B$4:$B$272, "1")</f>
@@ -4061,7 +4070,7 @@
         <v>45</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C15" s="33">
         <f>COUNTIF('통합테스트 시나리오'!$B$4:$B$272, "2")</f>
@@ -4069,7 +4078,7 @@
       </c>
       <c r="D15" s="59">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "2", '통합테스트 시나리오'!$M$4:$M$272, "Pass")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" s="60">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "2", '통합테스트 시나리오'!$M$4:$M$272, "Fail")</f>
@@ -4077,7 +4086,7 @@
       </c>
       <c r="F15" s="33">
         <f>C15-D15-E15</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="61">
         <f>IFERROR(D15/(D15+E15), 0)</f>
@@ -4089,7 +4098,7 @@
         <v>46</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C16" s="33">
         <f>COUNTIF('통합테스트 시나리오'!$B$4:$B$272, "3")</f>
@@ -4117,7 +4126,7 @@
         <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="C17" s="33">
         <f>COUNTIF('통합테스트 시나리오'!$B$4:$B$272, "4")</f>
@@ -4141,15 +4150,15 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="24" customHeight="1">
-      <c r="A19" s="106" t="s">
+      <c r="A19" s="109" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="106"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="106"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="106"/>
+      <c r="B19" s="109"/>
+      <c r="C19" s="109"/>
+      <c r="D19" s="109"/>
+      <c r="E19" s="109"/>
+      <c r="F19" s="109"/>
+      <c r="G19" s="109"/>
     </row>
     <row r="20" spans="1:7" ht="27.75" customHeight="1">
       <c r="A20" s="4" t="s">
@@ -4176,13 +4185,13 @@
     </row>
     <row r="21" spans="1:7" ht="24" customHeight="1">
       <c r="A21" s="32" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="D21" s="33">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-02-P", '통합테스트 시나리오'!$P$4:$P$272)))*1)</f>
@@ -4203,13 +4212,13 @@
     </row>
     <row r="22" spans="1:7" ht="24" customHeight="1">
       <c r="A22" s="32" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="D22" s="33">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-02-R", '통합테스트 시나리오'!$P$4:$P$272)))*1)</f>
@@ -4233,10 +4242,10 @@
         <v>189</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D23" s="33">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-03", '통합테스트 시나리오'!$P$4:$P$272)))*1)</f>
@@ -4257,21 +4266,21 @@
     </row>
     <row r="24" spans="1:7" ht="24" customHeight="1">
       <c r="A24" s="32" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D24" s="33">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-06", '통합테스트 시나리오'!$P$4:$P$272)))*1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="59">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-06", '통합테스트 시나리오'!$P$4:$P$272)))*('통합테스트 시나리오'!$M$4:$M$272="Pass"))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="60">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-06", '통합테스트 시나리오'!$P$4:$P$272)))*('통합테스트 시나리오'!$M$4:$M$272="Fail"))</f>
@@ -4284,13 +4293,13 @@
     </row>
     <row r="25" spans="1:7" ht="24" customHeight="1">
       <c r="A25" s="32" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="D25" s="33">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-07", '통합테스트 시나리오'!$P$4:$P$272)))*1)</f>
@@ -4319,15 +4328,15 @@
       <c r="G26" s="61"/>
     </row>
     <row r="28" spans="1:7" ht="24" customHeight="1">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="106"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
+      <c r="B28" s="109"/>
+      <c r="C28" s="109"/>
+      <c r="D28" s="109"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="109"/>
     </row>
     <row r="29" spans="1:7" ht="25.5" customHeight="1">
       <c r="A29" s="1" t="s">
@@ -4352,7 +4361,7 @@
     </row>
     <row r="30" spans="1:7" ht="21.75" customHeight="1">
       <c r="A30" s="25" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="B30" s="35" t="s">
         <v>101</v>
@@ -4365,7 +4374,7 @@
         <v>100</v>
       </c>
       <c r="E30" s="35" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="F30" s="36">
         <f>COUNTIF(수정사항관리!$K$5:$K$200, "진행 중")</f>
@@ -4374,7 +4383,7 @@
     </row>
     <row r="31" spans="1:7" ht="21.75" customHeight="1">
       <c r="A31" s="25" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="B31" s="35" t="s">
         <v>102</v>
@@ -4396,10 +4405,10 @@
     </row>
     <row r="32" spans="1:7" ht="21.75" customHeight="1">
       <c r="A32" s="25" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="B32" s="35" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C32" s="36">
         <f>COUNTIF(수정사항관리!$E$5:$E$200, "추가")+COUNTIF(수정사항관리!$E$5:$E$200, "검토")</f>
@@ -4417,41 +4426,36 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="25.5" customHeight="1">
-      <c r="A33" s="107" t="s">
-        <v>365</v>
-      </c>
-      <c r="B33" s="107"/>
+      <c r="A33" s="110" t="s">
+        <v>353</v>
+      </c>
+      <c r="B33" s="110"/>
       <c r="C33" s="37">
         <f>COUNTA(수정사항관리!$B$5:$B$200)</f>
         <v>19</v>
       </c>
-      <c r="D33" s="107" t="s">
-        <v>365</v>
-      </c>
-      <c r="E33" s="107"/>
+      <c r="D33" s="110" t="s">
+        <v>353</v>
+      </c>
+      <c r="E33" s="110"/>
       <c r="F33" s="37">
         <f>COUNTA(수정사항관리!$B$5:$B$200)</f>
         <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1">
-      <c r="A35" s="108" t="s">
+      <c r="A35" s="111" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="108"/>
-      <c r="C35" s="108"/>
-      <c r="D35" s="108"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="108"/>
-      <c r="G35" s="108"/>
+      <c r="B35" s="111"/>
+      <c r="C35" s="111"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="111"/>
+      <c r="F35" s="111"/>
+      <c r="G35" s="111"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:G4"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="D33:E33"/>
@@ -4461,6 +4465,11 @@
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:G4"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4495,16 +4504,16 @@
       <c r="H1" s="112"/>
     </row>
     <row r="2" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="111" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1">
       <c r="A3" s="4" t="s">
@@ -4537,7 +4546,7 @@
         <v>61</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="C4" s="37"/>
       <c r="D4" s="37">
@@ -4598,7 +4607,7 @@
         <v>62</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="C7" s="37"/>
       <c r="D7" s="37">
@@ -4752,7 +4761,7 @@
         <v>63</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C13" s="37"/>
       <c r="D13" s="37">
@@ -4761,7 +4770,7 @@
       </c>
       <c r="E13" s="37">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "2", '통합테스트 시나리오'!$M$4:$M$272, "Pass")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="37">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "2", '통합테스트 시나리오'!$M$4:$M$272, "Fail")</f>
@@ -4769,7 +4778,7 @@
       </c>
       <c r="G13" s="37">
         <f t="shared" ref="G13:G18" si="0">D13-E13-F13</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="39">
         <f t="shared" ref="H13:H18" si="1">IFERROR(E13/(E13+F13), 0)</f>
@@ -4823,7 +4832,7 @@
       </c>
       <c r="E15" s="42">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "2", '통합테스트 시나리오'!$E$4:$E$272, C15, '통합테스트 시나리오'!$M$4:$M$272, "Pass")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="43">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "2", '통합테스트 시나리오'!$E$4:$E$272, C15, '통합테스트 시나리오'!$M$4:$M$272, "Fail")</f>
@@ -4831,7 +4840,7 @@
       </c>
       <c r="G15" s="62">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="44">
         <f t="shared" si="1"/>
@@ -4843,10 +4852,10 @@
         <v>3</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D16" s="41">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "2", '통합테스트 시나리오'!$E$4:$E$272, C16)</f>
@@ -4874,10 +4883,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D17" s="41">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "2", '통합테스트 시나리오'!$E$4:$E$272, C17)</f>
@@ -4905,10 +4914,10 @@
         <v>5</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D18" s="41">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "2", '통합테스트 시나리오'!$E$4:$E$272, C18)</f>
@@ -4937,7 +4946,7 @@
         <v>64</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37">
@@ -4966,10 +4975,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D21" s="41">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "3", '통합테스트 시나리오'!$E$4:$E$272, C21)</f>
@@ -4997,10 +5006,10 @@
         <v>2</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D22" s="41">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "3", '통합테스트 시나리오'!$E$4:$E$272, C22)</f>
@@ -5029,7 +5038,7 @@
         <v>65</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C24" s="37"/>
       <c r="D24" s="37">
@@ -5058,10 +5067,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D25" s="41">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "4", '통합테스트 시나리오'!$E$4:$E$272, C25)</f>
@@ -5089,10 +5098,10 @@
         <v>2</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D26" s="41">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "4", '통합테스트 시나리오'!$E$4:$E$272, C26)</f>
@@ -5764,7 +5773,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="175">
+    <row r="17" spans="2:16" ht="245">
       <c r="B17" s="18">
         <v>2</v>
       </c>
@@ -5782,28 +5791,30 @@
         <v>191</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>192</v>
+        <v>417</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>193</v>
+        <v>416</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>194</v>
+        <v>415</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>195</v>
+        <v>414</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="M17" s="20"/>
+        <v>413</v>
+      </c>
+      <c r="M17" s="20" t="s">
+        <v>34</v>
+      </c>
       <c r="N17" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="O17" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="P17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="18" spans="2:16" ht="280">
       <c r="B18" s="18">
@@ -5814,28 +5825,28 @@
         <v>12</v>
       </c>
       <c r="E18" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="K18" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="L18" s="20" t="s">
         <v>199</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="I18" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="J18" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="K18" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="L18" s="20" t="s">
-        <v>205</v>
       </c>
       <c r="M18" s="20" t="s">
         <v>34</v>
@@ -5859,28 +5870,28 @@
         <v>13</v>
       </c>
       <c r="E19" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="K19" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="L19" s="20" t="s">
         <v>207</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="H19" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="I19" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="J19" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="K19" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="L19" s="20" t="s">
-        <v>213</v>
       </c>
       <c r="M19" s="20" t="s">
         <v>34</v>
@@ -5900,28 +5911,28 @@
         <v>14</v>
       </c>
       <c r="E20" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="K20" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="L20" s="20" t="s">
         <v>215</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="H20" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="I20" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="J20" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="K20" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="L20" s="20" t="s">
-        <v>221</v>
       </c>
       <c r="M20" s="20" t="s">
         <v>34</v>
@@ -5930,7 +5941,7 @@
         <v>106</v>
       </c>
       <c r="O20" s="20" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="P20" s="20"/>
     </row>
@@ -5938,7 +5949,7 @@
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
       <c r="D21" s="19" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E21" s="20"/>
       <c r="F21" s="20"/>
@@ -5962,28 +5973,28 @@
         <v>15</v>
       </c>
       <c r="E22" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="K22" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="L22" s="20" t="s">
         <v>225</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="H22" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="I22" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="J22" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="K22" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="L22" s="20" t="s">
-        <v>231</v>
       </c>
       <c r="M22" s="20" t="s">
         <v>34</v>
@@ -6003,28 +6014,28 @@
         <v>16</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F23" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="L23" s="20" t="s">
         <v>232</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="I23" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="J23" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="K23" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="L23" s="20" t="s">
-        <v>238</v>
       </c>
       <c r="M23" s="20" t="s">
         <v>34</v>
@@ -6044,28 +6055,28 @@
         <v>17</v>
       </c>
       <c r="E24" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="K24" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="L24" s="20" t="s">
         <v>240</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="I24" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="J24" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="K24" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="L24" s="20" t="s">
-        <v>246</v>
       </c>
       <c r="M24" s="20" t="s">
         <v>34</v>
@@ -6076,7 +6087,7 @@
       <c r="O24" s="20"/>
       <c r="P24" s="20"/>
     </row>
-    <row r="25" spans="2:16" ht="140">
+    <row r="25" spans="2:16" ht="192.5">
       <c r="B25" s="18">
         <v>3</v>
       </c>
@@ -6085,37 +6096,37 @@
         <v>18</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>249</v>
+        <v>424</v>
       </c>
       <c r="I25" s="20" t="s">
-        <v>250</v>
+        <v>423</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>251</v>
+        <v>422</v>
       </c>
       <c r="K25" s="20" t="s">
-        <v>252</v>
+        <v>421</v>
       </c>
       <c r="L25" s="20" t="s">
-        <v>253</v>
+        <v>420</v>
       </c>
       <c r="M25" s="20" t="s">
-        <v>34</v>
+        <v>419</v>
       </c>
       <c r="N25" s="20" t="s">
         <v>106</v>
       </c>
       <c r="O25" s="20" t="s">
-        <v>254</v>
+        <v>418</v>
       </c>
       <c r="P25" s="20"/>
     </row>
@@ -6128,28 +6139,28 @@
         <v>19</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="I26" s="20" t="s">
         <v>150</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="K26" s="20" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="L26" s="20" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="M26" s="20" t="s">
         <v>34</v>
@@ -6158,7 +6169,7 @@
         <v>106</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="P26" s="20"/>
     </row>
@@ -6171,28 +6182,28 @@
         <v>20</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="I27" s="20" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="K27" s="20" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="L27" s="20" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="M27" s="20" t="s">
         <v>34</v>
@@ -6201,7 +6212,7 @@
         <v>106</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="P27" s="20"/>
     </row>
@@ -6209,7 +6220,7 @@
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
       <c r="D28" s="19" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="E28" s="20"/>
       <c r="F28" s="20"/>
@@ -6233,28 +6244,28 @@
         <v>21</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="I29" s="20" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="K29" s="20" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="L29" s="20" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="M29" s="20" t="s">
         <v>34</v>
@@ -6264,7 +6275,7 @@
       </c>
       <c r="O29" s="20"/>
       <c r="P29" s="20" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="70">
@@ -6276,28 +6287,28 @@
         <v>22</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="I30" s="20" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="K30" s="20" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="L30" s="20" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="M30" s="20" t="s">
         <v>34</v>
@@ -6319,28 +6330,28 @@
         <v>23</v>
       </c>
       <c r="E31" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="J31" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="F31" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="H31" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="I31" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="J31" s="20" t="s">
-        <v>292</v>
-      </c>
       <c r="K31" s="20" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="L31" s="20" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="M31" s="20" t="s">
         <v>34</v>
@@ -6349,7 +6360,7 @@
         <v>106</v>
       </c>
       <c r="O31" s="20" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="P31" s="20" t="s">
         <v>189</v>
@@ -6364,28 +6375,28 @@
         <v>24</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="I32" s="20" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="K32" s="20" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="L32" s="20" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="M32" s="20" t="s">
         <v>34</v>
@@ -6397,7 +6408,7 @@
         <v>188</v>
       </c>
       <c r="P32" s="20" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="87.5">
@@ -6409,28 +6420,28 @@
         <v>25</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="I33" s="20" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="K33" s="20" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="L33" s="20" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="M33" s="20" t="s">
         <v>34</v>
@@ -6440,7 +6451,7 @@
       </c>
       <c r="O33" s="20"/>
       <c r="P33" s="20" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="175">
@@ -6452,28 +6463,28 @@
         <v>26</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="J34" s="20" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="K34" s="20" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="L34" s="20" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="M34" s="20" t="s">
         <v>34</v>
@@ -6483,7 +6494,7 @@
       </c>
       <c r="O34" s="20"/>
       <c r="P34" s="20" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="140">
@@ -6495,28 +6506,28 @@
         <v>27</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="I35" s="20" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="K35" s="20" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="L35" s="20" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="M35" s="20" t="s">
         <v>34</v>
@@ -6526,7 +6537,7 @@
       </c>
       <c r="O35" s="20"/>
       <c r="P35" s="20" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="36" customHeight="1">
@@ -10646,28 +10657,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="115" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
+      <c r="A1" s="113" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="108" t="s">
-        <v>333</v>
-      </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
+      <c r="A2" s="111" t="s">
+        <v>321</v>
+      </c>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1">
       <c r="A3" s="4" t="s">
@@ -10697,16 +10708,16 @@
     </row>
     <row r="4" spans="1:8" ht="27.75" customHeight="1">
       <c r="A4" s="63" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="E4" s="33">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-02-P", '통합테스트 시나리오'!$P$4:$P$272)))*1)</f>
@@ -10727,16 +10738,16 @@
     </row>
     <row r="5" spans="1:8" ht="27.75" customHeight="1">
       <c r="A5" s="63" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="E5" s="33">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-02-R", '통합테스트 시나리오'!$P$4:$P$272)))*1)</f>
@@ -10760,13 +10771,13 @@
         <v>189</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="E6" s="33">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-03", '통합테스트 시나리오'!$P$4:$P$272)))*1)</f>
@@ -10787,24 +10798,24 @@
     </row>
     <row r="7" spans="1:8" ht="27.75" customHeight="1">
       <c r="A7" s="63" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="E7" s="33">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-06", '통합테스트 시나리오'!$P$4:$P$272)))*1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="59">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-06", '통합테스트 시나리오'!$P$4:$P$272)))*('통합테스트 시나리오'!$M$4:$M$272="Pass"))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="60">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-06", '통합테스트 시나리오'!$P$4:$P$272)))*('통합테스트 시나리오'!$M$4:$M$272="Fail"))</f>
@@ -10817,16 +10828,16 @@
     </row>
     <row r="8" spans="1:8" ht="27.75" customHeight="1">
       <c r="A8" s="63" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="E8" s="33">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("IF-07", '통합테스트 시나리오'!$P$4:$P$272)))*1)</f>
@@ -10856,19 +10867,19 @@
       <c r="H9" s="61"/>
     </row>
     <row r="11" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A11" s="107" t="s">
+      <c r="A11" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="107"/>
-      <c r="C11" s="107"/>
-      <c r="D11" s="107"/>
+      <c r="B11" s="110"/>
+      <c r="C11" s="110"/>
+      <c r="D11" s="110"/>
       <c r="E11" s="37">
         <f>SUM(E4:E9)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" s="37">
         <f>SUM(F4:F9)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" s="37">
         <f>SUM(G4:G9)</f>
@@ -10885,92 +10896,87 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A14" s="113" t="s">
-        <v>345</v>
-      </c>
-      <c r="B14" s="113"/>
-      <c r="C14" s="114" t="s">
-        <v>346</v>
-      </c>
-      <c r="D14" s="114"/>
-      <c r="E14" s="114"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="114"/>
+      <c r="A14" s="114" t="s">
+        <v>333</v>
+      </c>
+      <c r="B14" s="114"/>
+      <c r="C14" s="115" t="s">
+        <v>334</v>
+      </c>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
     </row>
     <row r="15" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A15" s="113" t="s">
-        <v>347</v>
-      </c>
-      <c r="B15" s="113"/>
-      <c r="C15" s="114" t="s">
-        <v>348</v>
-      </c>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="114"/>
+      <c r="A15" s="114" t="s">
+        <v>335</v>
+      </c>
+      <c r="B15" s="114"/>
+      <c r="C15" s="115" t="s">
+        <v>336</v>
+      </c>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
     </row>
     <row r="16" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A16" s="113" t="s">
-        <v>349</v>
-      </c>
-      <c r="B16" s="113"/>
-      <c r="C16" s="114" t="s">
-        <v>350</v>
-      </c>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="114"/>
-      <c r="G16" s="114"/>
-      <c r="H16" s="114"/>
+      <c r="A16" s="114" t="s">
+        <v>337</v>
+      </c>
+      <c r="B16" s="114"/>
+      <c r="C16" s="115" t="s">
+        <v>338</v>
+      </c>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
     </row>
     <row r="17" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A17" s="113" t="s">
-        <v>351</v>
-      </c>
-      <c r="B17" s="113"/>
-      <c r="C17" s="114" t="s">
-        <v>352</v>
-      </c>
-      <c r="D17" s="114"/>
-      <c r="E17" s="114"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="114"/>
+      <c r="A17" s="114" t="s">
+        <v>339</v>
+      </c>
+      <c r="B17" s="114"/>
+      <c r="C17" s="115" t="s">
+        <v>340</v>
+      </c>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
     </row>
     <row r="18" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A18" s="113" t="s">
-        <v>353</v>
-      </c>
-      <c r="B18" s="113"/>
-      <c r="C18" s="114" t="s">
-        <v>354</v>
-      </c>
-      <c r="D18" s="114"/>
-      <c r="E18" s="114"/>
-      <c r="F18" s="114"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="114"/>
+      <c r="A18" s="114" t="s">
+        <v>341</v>
+      </c>
+      <c r="B18" s="114"/>
+      <c r="C18" s="115" t="s">
+        <v>342</v>
+      </c>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
     </row>
     <row r="19" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A19" s="113"/>
-      <c r="B19" s="113"/>
-      <c r="C19" s="114"/>
-      <c r="D19" s="114"/>
-      <c r="E19" s="114"/>
-      <c r="F19" s="114"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="114"/>
+      <c r="A19" s="114"/>
+      <c r="B19" s="114"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:H14"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="A19:B19"/>
@@ -10981,6 +10987,11 @@
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C17:H17"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:H14"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11030,7 +11041,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="D2" s="52"/>
       <c r="E2" s="50" t="s">
@@ -11043,7 +11054,7 @@
         <v>67</v>
       </c>
       <c r="I2" s="53" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="J2" s="86"/>
       <c r="L2" s="50" t="s">
@@ -11090,7 +11101,7 @@
     </row>
     <row r="4" spans="1:12" ht="16.5" customHeight="1">
       <c r="A4" s="95" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="B4" s="96"/>
       <c r="C4" s="96"/>
@@ -11112,10 +11123,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D5" s="55" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="E5" s="55" t="s">
         <v>24</v>
@@ -11139,7 +11150,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="55" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="56" customFormat="1" ht="32">
@@ -11150,10 +11161,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="E6" s="57" t="s">
         <v>24</v>
@@ -11177,7 +11188,7 @@
         <v>7</v>
       </c>
       <c r="L6" s="57" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="56" customFormat="1" ht="32">
@@ -11188,10 +11199,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="D7" s="55" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E7" s="55" t="s">
         <v>22</v>
@@ -11215,7 +11226,7 @@
         <v>7</v>
       </c>
       <c r="L7" s="55" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="56" customFormat="1">
@@ -11229,7 +11240,7 @@
         <v>180</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="E8" s="57" t="s">
         <v>22</v>
@@ -11253,7 +11264,7 @@
         <v>7</v>
       </c>
       <c r="L8" s="57" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="56" customFormat="1" ht="32">
@@ -11264,10 +11275,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="E9" s="55" t="s">
         <v>24</v>
@@ -11291,7 +11302,7 @@
         <v>7</v>
       </c>
       <c r="L9" s="55" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="56" customFormat="1">
@@ -11302,10 +11313,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="E10" s="57" t="s">
         <v>24</v>
@@ -11338,10 +11349,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="E11" s="55" t="s">
         <v>22</v>
@@ -11377,7 +11388,7 @@
         <v>180</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="E12" s="57" t="s">
         <v>24</v>
@@ -11401,7 +11412,7 @@
         <v>7</v>
       </c>
       <c r="L12" s="57" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="56" customFormat="1" ht="32">
@@ -11412,10 +11423,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="E13" s="55" t="s">
         <v>24</v>
@@ -11439,7 +11450,7 @@
         <v>7</v>
       </c>
       <c r="L13" s="55" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="56" customFormat="1" ht="32">
@@ -11450,10 +11461,10 @@
         <v>10</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="E14" s="57" t="s">
         <v>24</v>
@@ -11477,7 +11488,7 @@
         <v>7</v>
       </c>
       <c r="L14" s="57" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="56" customFormat="1" ht="48">
@@ -11488,10 +11499,10 @@
         <v>11</v>
       </c>
       <c r="C15" s="55" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D15" s="55" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="E15" s="55" t="s">
         <v>24</v>
@@ -11515,7 +11526,7 @@
         <v>7</v>
       </c>
       <c r="L15" s="55" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="56" customFormat="1" ht="32">
@@ -11526,10 +11537,10 @@
         <v>12</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="D16" s="57" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E16" s="57" t="s">
         <v>22</v>
@@ -11553,7 +11564,7 @@
         <v>7</v>
       </c>
       <c r="L16" s="57" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="56" customFormat="1" ht="32">
@@ -11564,10 +11575,10 @@
         <v>13</v>
       </c>
       <c r="C17" s="55" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="D17" s="55" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="E17" s="55" t="s">
         <v>24</v>
@@ -11591,7 +11602,7 @@
         <v>7</v>
       </c>
       <c r="L17" s="55" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="56" customFormat="1" ht="32">
@@ -11602,10 +11613,10 @@
         <v>14</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="E18" s="57" t="s">
         <v>24</v>
@@ -11629,7 +11640,7 @@
         <v>7</v>
       </c>
       <c r="L18" s="57" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="56" customFormat="1" ht="32">
@@ -11640,10 +11651,10 @@
         <v>15</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="D19" s="55" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="E19" s="55" t="s">
         <v>24</v>
@@ -11667,7 +11678,7 @@
         <v>7</v>
       </c>
       <c r="L19" s="55" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="56" customFormat="1" ht="32">
@@ -11678,10 +11689,10 @@
         <v>16</v>
       </c>
       <c r="C20" s="57" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="D20" s="57" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="E20" s="57" t="s">
         <v>24</v>
@@ -11705,7 +11716,7 @@
         <v>7</v>
       </c>
       <c r="L20" s="57" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="56" customFormat="1">
@@ -11716,10 +11727,10 @@
         <v>17</v>
       </c>
       <c r="C21" s="55" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="D21" s="55" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="E21" s="55" t="s">
         <v>24</v>
@@ -11743,7 +11754,7 @@
         <v>7</v>
       </c>
       <c r="L21" s="55" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="56" customFormat="1" ht="32">
@@ -11754,10 +11765,10 @@
         <v>18</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="D22" s="57" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="E22" s="57" t="s">
         <v>22</v>
@@ -11781,7 +11792,7 @@
         <v>7</v>
       </c>
       <c r="L22" s="57" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="56" customFormat="1">
@@ -11792,10 +11803,10 @@
         <v>19</v>
       </c>
       <c r="C23" s="55" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="D23" s="55" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="E23" s="55" t="s">
         <v>24</v>
@@ -11819,7 +11830,7 @@
         <v>7</v>
       </c>
       <c r="L23" s="55" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="56" customFormat="1">
@@ -13370,6 +13381,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="355e9163-e205-4f55-8724-e062aa2d762e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b82e25f1-f1d4-4b57-be84-1f5ad188becc" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x01010065F9ABE2E9073F4DBEFD3A0E4E804736" ma:contentTypeVersion="15" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="e21f2c0381dcdb676ff4d058d9391828">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="355e9163-e205-4f55-8724-e062aa2d762e" xmlns:ns3="b82e25f1-f1d4-4b57-be84-1f5ad188becc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74ede542eddc1547cf48ce9271227341" ns2:_="" ns3:_="">
     <xsd:import namespace="355e9163-e205-4f55-8724-e062aa2d762e"/>
@@ -13604,26 +13634,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{864945DC-F2EC-4FA1-9FED-44C14AFD68C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="355e9163-e205-4f55-8724-e062aa2d762e"/>
+    <ds:schemaRef ds:uri="b82e25f1-f1d4-4b57-be84-1f5ad188becc"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="355e9163-e205-4f55-8724-e062aa2d762e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b82e25f1-f1d4-4b57-be84-1f5ad188becc" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{418FC364-5D1D-4139-96C0-59534BD84D4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FAD5F7D-B2A1-44B1-ADEC-D6D3F0B82DF7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13640,23 +13670,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{418FC364-5D1D-4139-96C0-59534BD84D4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{864945DC-F2EC-4FA1-9FED-44C14AFD68C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="355e9163-e205-4f55-8724-e062aa2d762e"/>
-    <ds:schemaRef ds:uri="b82e25f1-f1d4-4b57-be84-1f5ad188becc"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>